--- a/data/mag 7 and above eruptions.xlsx
+++ b/data/mag 7 and above eruptions.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eart0428\Google Drive\Catastrophic volcanic eruptions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cassidmz\My Drive\Catastrophic volcanic eruptions\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C572E44-BED6-4CB3-B28C-4C3A98FD7D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22992" windowHeight="8568"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VOGRIPA" sheetId="1" r:id="rId1"/>
@@ -1029,7 +1030,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1191,7 +1192,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1374,6 +1375,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1597,7 +1604,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1652,6 +1659,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="11" xfId="6" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1972,7 +1990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BU166"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -22663,2449 +22681,2449 @@
         <v>45</v>
       </c>
     </row>
-    <row r="150" spans="1:73" s="3" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="A150" s="6" t="s">
+    <row r="150" spans="1:73" s="25" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="A150" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B150" s="4">
+      <c r="B150" s="23">
         <v>311350</v>
       </c>
-      <c r="C150" s="5">
+      <c r="C150" s="24">
         <v>54.65</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150" s="23">
         <v>-164.43333329999999</v>
       </c>
-      <c r="E150" s="5" t="s">
+      <c r="E150" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F150" s="4" t="s">
+      <c r="F150" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H150" s="4" t="s">
+      <c r="H150" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="I150" s="5"/>
-      <c r="J150" s="5"/>
-      <c r="K150" s="4"/>
-      <c r="L150" s="4">
+      <c r="I150" s="24"/>
+      <c r="J150" s="24"/>
+      <c r="K150" s="23"/>
+      <c r="L150" s="23">
         <v>10672</v>
       </c>
-      <c r="M150" s="4"/>
-      <c r="N150" s="4" t="s">
+      <c r="M150" s="23"/>
+      <c r="N150" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O150" s="4" t="s">
+      <c r="O150" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="P150" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q150" s="5"/>
-      <c r="R150" s="5"/>
-      <c r="S150" s="5"/>
-      <c r="T150" s="5"/>
-      <c r="U150" s="5"/>
-      <c r="V150" s="5"/>
-      <c r="W150" s="5"/>
-      <c r="X150" s="5"/>
-      <c r="Y150" s="5"/>
-      <c r="Z150" s="5"/>
-      <c r="AA150" s="5"/>
-      <c r="AB150" s="5"/>
-      <c r="AC150" s="5"/>
-      <c r="AD150" s="5"/>
-      <c r="AE150" s="5"/>
-      <c r="AF150" s="5"/>
-      <c r="AG150" s="5"/>
-      <c r="AH150" s="5"/>
-      <c r="AI150" s="5"/>
-      <c r="AJ150" s="5"/>
-      <c r="AK150" s="5"/>
-      <c r="AL150" s="5"/>
-      <c r="AM150" s="5"/>
-      <c r="AN150" s="5"/>
-      <c r="AO150" s="5"/>
-      <c r="AP150" s="5"/>
-      <c r="AQ150" s="5"/>
-      <c r="AR150" s="5"/>
-      <c r="AS150" s="5"/>
-      <c r="AT150" s="5">
+      <c r="P150" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q150" s="24"/>
+      <c r="R150" s="24"/>
+      <c r="S150" s="24"/>
+      <c r="T150" s="24"/>
+      <c r="U150" s="24"/>
+      <c r="V150" s="24"/>
+      <c r="W150" s="24"/>
+      <c r="X150" s="24"/>
+      <c r="Y150" s="24"/>
+      <c r="Z150" s="24"/>
+      <c r="AA150" s="24"/>
+      <c r="AB150" s="24"/>
+      <c r="AC150" s="24"/>
+      <c r="AD150" s="24"/>
+      <c r="AE150" s="24"/>
+      <c r="AF150" s="24"/>
+      <c r="AG150" s="24"/>
+      <c r="AH150" s="24"/>
+      <c r="AI150" s="24"/>
+      <c r="AJ150" s="24"/>
+      <c r="AK150" s="24"/>
+      <c r="AL150" s="24"/>
+      <c r="AM150" s="24"/>
+      <c r="AN150" s="24"/>
+      <c r="AO150" s="24"/>
+      <c r="AP150" s="24"/>
+      <c r="AQ150" s="24"/>
+      <c r="AR150" s="24"/>
+      <c r="AS150" s="24"/>
+      <c r="AT150" s="24">
         <v>142</v>
       </c>
-      <c r="AU150" s="5"/>
-      <c r="AV150" s="5">
+      <c r="AU150" s="24"/>
+      <c r="AV150" s="24">
         <v>117</v>
       </c>
-      <c r="AW150" s="5" t="s">
+      <c r="AW150" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AX150" s="5" t="s">
+      <c r="AX150" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY150" s="5">
+      <c r="AY150" s="24">
         <v>55</v>
       </c>
-      <c r="AZ150" s="5"/>
-      <c r="BA150" s="5">
-        <v>45</v>
-      </c>
-      <c r="BB150" s="5">
+      <c r="AZ150" s="24"/>
+      <c r="BA150" s="24">
+        <v>45</v>
+      </c>
+      <c r="BB150" s="24">
         <v>1</v>
       </c>
-      <c r="BC150" s="5" t="s">
+      <c r="BC150" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD150" s="4" t="s">
+      <c r="BD150" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="BE150" s="4"/>
-      <c r="BF150" s="5">
+      <c r="BE150" s="23"/>
+      <c r="BF150" s="24">
         <v>7.2</v>
       </c>
-      <c r="BG150" s="5"/>
-      <c r="BH150" s="5" t="s">
+      <c r="BG150" s="24"/>
+      <c r="BH150" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI150" s="5" t="s">
+      <c r="BI150" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ150" s="5">
+      <c r="BJ150" s="24">
         <v>7</v>
       </c>
-      <c r="BK150" s="5"/>
-      <c r="BL150" s="5" t="s">
+      <c r="BK150" s="24"/>
+      <c r="BL150" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM150" s="5" t="s">
+      <c r="BM150" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BN150" s="5"/>
-      <c r="BO150" s="5">
+      <c r="BN150" s="24"/>
+      <c r="BO150" s="24">
         <v>22</v>
       </c>
-      <c r="BP150" s="5"/>
-      <c r="BQ150" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR150" s="5"/>
-      <c r="BS150" s="5">
+      <c r="BP150" s="24"/>
+      <c r="BQ150" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR150" s="24"/>
+      <c r="BS150" s="24">
         <v>10.7</v>
       </c>
-      <c r="BT150" s="5"/>
-      <c r="BU150" s="4" t="s">
+      <c r="BT150" s="24"/>
+      <c r="BU150" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:73" s="3" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="A151" s="6" t="s">
+    <row r="151" spans="1:73" s="25" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="A151" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B151" s="4">
+      <c r="B151" s="23">
         <v>311350</v>
       </c>
-      <c r="C151" s="5">
+      <c r="C151" s="24">
         <v>54.65</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151" s="23">
         <v>-164.43333329999999</v>
       </c>
-      <c r="E151" s="5" t="s">
+      <c r="E151" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="F151" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H151" s="4" t="s">
+      <c r="H151" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="I151" s="5"/>
-      <c r="J151" s="5"/>
-      <c r="K151" s="4"/>
-      <c r="L151" s="4">
+      <c r="I151" s="24"/>
+      <c r="J151" s="24"/>
+      <c r="K151" s="23"/>
+      <c r="L151" s="23">
         <v>10672</v>
       </c>
-      <c r="M151" s="4"/>
-      <c r="N151" s="4" t="s">
+      <c r="M151" s="23"/>
+      <c r="N151" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O151" s="4" t="s">
+      <c r="O151" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="P151" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q151" s="5"/>
-      <c r="R151" s="5"/>
-      <c r="S151" s="5"/>
-      <c r="T151" s="5"/>
-      <c r="U151" s="5"/>
-      <c r="V151" s="5"/>
-      <c r="W151" s="5"/>
-      <c r="X151" s="5"/>
-      <c r="Y151" s="5"/>
-      <c r="Z151" s="5"/>
-      <c r="AA151" s="5"/>
-      <c r="AB151" s="5"/>
-      <c r="AC151" s="5"/>
-      <c r="AD151" s="5"/>
-      <c r="AE151" s="5"/>
-      <c r="AF151" s="5"/>
-      <c r="AG151" s="5"/>
-      <c r="AH151" s="5"/>
-      <c r="AI151" s="5"/>
-      <c r="AJ151" s="5"/>
-      <c r="AK151" s="5"/>
-      <c r="AL151" s="5"/>
-      <c r="AM151" s="5"/>
-      <c r="AN151" s="5"/>
-      <c r="AO151" s="5"/>
-      <c r="AP151" s="5"/>
-      <c r="AQ151" s="5"/>
-      <c r="AR151" s="5"/>
-      <c r="AS151" s="5"/>
-      <c r="AT151" s="5">
+      <c r="P151" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q151" s="24"/>
+      <c r="R151" s="24"/>
+      <c r="S151" s="24"/>
+      <c r="T151" s="24"/>
+      <c r="U151" s="24"/>
+      <c r="V151" s="24"/>
+      <c r="W151" s="24"/>
+      <c r="X151" s="24"/>
+      <c r="Y151" s="24"/>
+      <c r="Z151" s="24"/>
+      <c r="AA151" s="24"/>
+      <c r="AB151" s="24"/>
+      <c r="AC151" s="24"/>
+      <c r="AD151" s="24"/>
+      <c r="AE151" s="24"/>
+      <c r="AF151" s="24"/>
+      <c r="AG151" s="24"/>
+      <c r="AH151" s="24"/>
+      <c r="AI151" s="24"/>
+      <c r="AJ151" s="24"/>
+      <c r="AK151" s="24"/>
+      <c r="AL151" s="24"/>
+      <c r="AM151" s="24"/>
+      <c r="AN151" s="24"/>
+      <c r="AO151" s="24"/>
+      <c r="AP151" s="24"/>
+      <c r="AQ151" s="24"/>
+      <c r="AR151" s="24"/>
+      <c r="AS151" s="24"/>
+      <c r="AT151" s="24">
         <v>142</v>
       </c>
-      <c r="AU151" s="5"/>
-      <c r="AV151" s="5">
+      <c r="AU151" s="24"/>
+      <c r="AV151" s="24">
         <v>117</v>
       </c>
-      <c r="AW151" s="5" t="s">
+      <c r="AW151" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AX151" s="5" t="s">
+      <c r="AX151" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY151" s="5">
+      <c r="AY151" s="24">
         <v>55</v>
       </c>
-      <c r="AZ151" s="5"/>
-      <c r="BA151" s="5">
-        <v>45</v>
-      </c>
-      <c r="BB151" s="5">
+      <c r="AZ151" s="24"/>
+      <c r="BA151" s="24">
+        <v>45</v>
+      </c>
+      <c r="BB151" s="24">
         <v>1</v>
       </c>
-      <c r="BC151" s="5" t="s">
+      <c r="BC151" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD151" s="4" t="s">
+      <c r="BD151" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="BE151" s="4"/>
-      <c r="BF151" s="5">
+      <c r="BE151" s="23"/>
+      <c r="BF151" s="24">
         <v>7.2</v>
       </c>
-      <c r="BG151" s="5"/>
-      <c r="BH151" s="5" t="s">
+      <c r="BG151" s="24"/>
+      <c r="BH151" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI151" s="5" t="s">
+      <c r="BI151" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ151" s="5">
+      <c r="BJ151" s="24">
         <v>7</v>
       </c>
-      <c r="BK151" s="5"/>
-      <c r="BL151" s="5" t="s">
+      <c r="BK151" s="24"/>
+      <c r="BL151" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM151" s="5" t="s">
+      <c r="BM151" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BN151" s="5"/>
-      <c r="BO151" s="5">
+      <c r="BN151" s="24"/>
+      <c r="BO151" s="24">
         <v>22</v>
       </c>
-      <c r="BP151" s="5"/>
-      <c r="BQ151" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR151" s="5"/>
-      <c r="BS151" s="5">
+      <c r="BP151" s="24"/>
+      <c r="BQ151" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR151" s="24"/>
+      <c r="BS151" s="24">
         <v>10.7</v>
       </c>
-      <c r="BT151" s="5"/>
-      <c r="BU151" s="4" t="s">
+      <c r="BT151" s="24"/>
+      <c r="BU151" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="152" spans="1:73" s="3" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="A152" s="6" t="s">
+    <row r="152" spans="1:73" s="25" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="A152" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="B152" s="4">
+      <c r="B152" s="23">
         <v>311350</v>
       </c>
-      <c r="C152" s="5">
+      <c r="C152" s="24">
         <v>54.65</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152" s="23">
         <v>-164.43333329999999</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="E152" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F152" s="4" t="s">
+      <c r="F152" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G152" s="4" t="s">
+      <c r="G152" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H152" s="4" t="s">
+      <c r="H152" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="I152" s="5"/>
-      <c r="J152" s="5"/>
-      <c r="K152" s="4"/>
-      <c r="L152" s="4">
+      <c r="I152" s="24"/>
+      <c r="J152" s="24"/>
+      <c r="K152" s="23"/>
+      <c r="L152" s="23">
         <v>10672</v>
       </c>
-      <c r="M152" s="4"/>
-      <c r="N152" s="4" t="s">
+      <c r="M152" s="23"/>
+      <c r="N152" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O152" s="4" t="s">
+      <c r="O152" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="P152" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q152" s="5"/>
-      <c r="R152" s="5"/>
-      <c r="S152" s="5"/>
-      <c r="T152" s="5"/>
-      <c r="U152" s="5"/>
-      <c r="V152" s="5"/>
-      <c r="W152" s="5"/>
-      <c r="X152" s="5"/>
-      <c r="Y152" s="5"/>
-      <c r="Z152" s="5"/>
-      <c r="AA152" s="5"/>
-      <c r="AB152" s="5"/>
-      <c r="AC152" s="5"/>
-      <c r="AD152" s="5"/>
-      <c r="AE152" s="5"/>
-      <c r="AF152" s="5"/>
-      <c r="AG152" s="5"/>
-      <c r="AH152" s="5"/>
-      <c r="AI152" s="5"/>
-      <c r="AJ152" s="5"/>
-      <c r="AK152" s="5"/>
-      <c r="AL152" s="5"/>
-      <c r="AM152" s="5"/>
-      <c r="AN152" s="5"/>
-      <c r="AO152" s="5"/>
-      <c r="AP152" s="5"/>
-      <c r="AQ152" s="5"/>
-      <c r="AR152" s="5"/>
-      <c r="AS152" s="5"/>
-      <c r="AT152" s="5">
+      <c r="P152" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q152" s="24"/>
+      <c r="R152" s="24"/>
+      <c r="S152" s="24"/>
+      <c r="T152" s="24"/>
+      <c r="U152" s="24"/>
+      <c r="V152" s="24"/>
+      <c r="W152" s="24"/>
+      <c r="X152" s="24"/>
+      <c r="Y152" s="24"/>
+      <c r="Z152" s="24"/>
+      <c r="AA152" s="24"/>
+      <c r="AB152" s="24"/>
+      <c r="AC152" s="24"/>
+      <c r="AD152" s="24"/>
+      <c r="AE152" s="24"/>
+      <c r="AF152" s="24"/>
+      <c r="AG152" s="24"/>
+      <c r="AH152" s="24"/>
+      <c r="AI152" s="24"/>
+      <c r="AJ152" s="24"/>
+      <c r="AK152" s="24"/>
+      <c r="AL152" s="24"/>
+      <c r="AM152" s="24"/>
+      <c r="AN152" s="24"/>
+      <c r="AO152" s="24"/>
+      <c r="AP152" s="24"/>
+      <c r="AQ152" s="24"/>
+      <c r="AR152" s="24"/>
+      <c r="AS152" s="24"/>
+      <c r="AT152" s="24">
         <v>142</v>
       </c>
-      <c r="AU152" s="5"/>
-      <c r="AV152" s="5">
+      <c r="AU152" s="24"/>
+      <c r="AV152" s="24">
         <v>117</v>
       </c>
-      <c r="AW152" s="5" t="s">
+      <c r="AW152" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AX152" s="5" t="s">
+      <c r="AX152" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY152" s="5">
+      <c r="AY152" s="24">
         <v>55</v>
       </c>
-      <c r="AZ152" s="5"/>
-      <c r="BA152" s="5">
-        <v>45</v>
-      </c>
-      <c r="BB152" s="5">
+      <c r="AZ152" s="24"/>
+      <c r="BA152" s="24">
+        <v>45</v>
+      </c>
+      <c r="BB152" s="24">
         <v>1</v>
       </c>
-      <c r="BC152" s="5" t="s">
+      <c r="BC152" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD152" s="4" t="s">
+      <c r="BD152" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="BE152" s="4"/>
-      <c r="BF152" s="5">
+      <c r="BE152" s="23"/>
+      <c r="BF152" s="24">
         <v>7.2</v>
       </c>
-      <c r="BG152" s="5"/>
-      <c r="BH152" s="5" t="s">
+      <c r="BG152" s="24"/>
+      <c r="BH152" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI152" s="5" t="s">
+      <c r="BI152" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ152" s="5">
+      <c r="BJ152" s="24">
         <v>7</v>
       </c>
-      <c r="BK152" s="5"/>
-      <c r="BL152" s="5" t="s">
+      <c r="BK152" s="24"/>
+      <c r="BL152" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM152" s="5" t="s">
+      <c r="BM152" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BN152" s="5"/>
-      <c r="BO152" s="5">
+      <c r="BN152" s="24"/>
+      <c r="BO152" s="24">
         <v>22</v>
       </c>
-      <c r="BP152" s="5"/>
-      <c r="BQ152" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR152" s="5"/>
-      <c r="BS152" s="5">
+      <c r="BP152" s="24"/>
+      <c r="BQ152" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR152" s="24"/>
+      <c r="BS152" s="24">
         <v>10.7</v>
       </c>
-      <c r="BT152" s="5"/>
-      <c r="BU152" s="4" t="s">
+      <c r="BT152" s="24"/>
+      <c r="BU152" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A153" s="6" t="s">
+    <row r="153" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A153" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="B153" s="4">
+      <c r="B153" s="23">
         <v>311060</v>
       </c>
-      <c r="C153" s="5">
+      <c r="C153" s="24">
         <v>51.933333330000004</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153" s="23">
         <v>179.58333329999999</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="E153" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="F153" s="4" t="s">
+      <c r="F153" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G153" s="4" t="s">
+      <c r="G153" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H153" s="4" t="s">
+      <c r="H153" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="I153" s="5"/>
-      <c r="J153" s="5"/>
-      <c r="K153" s="4"/>
-      <c r="L153" s="4">
+      <c r="I153" s="24"/>
+      <c r="J153" s="24"/>
+      <c r="K153" s="23"/>
+      <c r="L153" s="23">
         <v>9950</v>
       </c>
-      <c r="M153" s="4"/>
-      <c r="N153" s="4" t="s">
+      <c r="M153" s="23"/>
+      <c r="N153" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="O153" s="4" t="s">
+      <c r="O153" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="P153" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q153" s="5"/>
-      <c r="R153" s="5"/>
-      <c r="S153" s="5"/>
-      <c r="T153" s="5"/>
-      <c r="U153" s="5"/>
-      <c r="V153" s="5"/>
-      <c r="W153" s="5"/>
-      <c r="X153" s="5"/>
-      <c r="Y153" s="5"/>
-      <c r="Z153" s="5"/>
-      <c r="AA153" s="5"/>
-      <c r="AB153" s="5"/>
-      <c r="AC153" s="5"/>
-      <c r="AD153" s="5"/>
-      <c r="AE153" s="5"/>
-      <c r="AF153" s="5"/>
-      <c r="AG153" s="5"/>
-      <c r="AH153" s="5"/>
-      <c r="AI153" s="5"/>
-      <c r="AJ153" s="5"/>
-      <c r="AK153" s="5"/>
-      <c r="AL153" s="5"/>
-      <c r="AM153" s="5"/>
-      <c r="AN153" s="5"/>
-      <c r="AO153" s="5"/>
-      <c r="AP153" s="5"/>
-      <c r="AQ153" s="5"/>
-      <c r="AR153" s="5"/>
-      <c r="AS153" s="5"/>
-      <c r="AT153" s="5">
+      <c r="P153" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q153" s="24"/>
+      <c r="R153" s="24"/>
+      <c r="S153" s="24"/>
+      <c r="T153" s="24"/>
+      <c r="U153" s="24"/>
+      <c r="V153" s="24"/>
+      <c r="W153" s="24"/>
+      <c r="X153" s="24"/>
+      <c r="Y153" s="24"/>
+      <c r="Z153" s="24"/>
+      <c r="AA153" s="24"/>
+      <c r="AB153" s="24"/>
+      <c r="AC153" s="24"/>
+      <c r="AD153" s="24"/>
+      <c r="AE153" s="24"/>
+      <c r="AF153" s="24"/>
+      <c r="AG153" s="24"/>
+      <c r="AH153" s="24"/>
+      <c r="AI153" s="24"/>
+      <c r="AJ153" s="24"/>
+      <c r="AK153" s="24"/>
+      <c r="AL153" s="24"/>
+      <c r="AM153" s="24"/>
+      <c r="AN153" s="24"/>
+      <c r="AO153" s="24"/>
+      <c r="AP153" s="24"/>
+      <c r="AQ153" s="24"/>
+      <c r="AR153" s="24"/>
+      <c r="AS153" s="24"/>
+      <c r="AT153" s="24">
         <v>120</v>
       </c>
-      <c r="AU153" s="5"/>
-      <c r="AV153" s="5"/>
-      <c r="AW153" s="5">
+      <c r="AU153" s="24"/>
+      <c r="AV153" s="24"/>
+      <c r="AW153" s="24">
         <v>0</v>
       </c>
-      <c r="AX153" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY153" s="5">
+      <c r="AX153" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY153" s="24">
         <v>50</v>
       </c>
-      <c r="AZ153" s="5"/>
-      <c r="BA153" s="5"/>
-      <c r="BB153" s="5">
+      <c r="AZ153" s="24"/>
+      <c r="BA153" s="24"/>
+      <c r="BB153" s="24">
         <v>0</v>
       </c>
-      <c r="BC153" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD153" s="4" t="s">
+      <c r="BC153" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD153" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE153" s="4"/>
-      <c r="BF153" s="5">
+      <c r="BE153" s="23"/>
+      <c r="BF153" s="24">
         <v>7.1</v>
       </c>
-      <c r="BG153" s="5"/>
-      <c r="BH153" s="5" t="s">
+      <c r="BG153" s="24"/>
+      <c r="BH153" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BI153" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ153" s="5">
+      <c r="BI153" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ153" s="24">
         <v>7</v>
       </c>
-      <c r="BK153" s="5"/>
-      <c r="BL153" s="5" t="s">
+      <c r="BK153" s="24"/>
+      <c r="BL153" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM153" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN153" s="5"/>
-      <c r="BO153" s="5"/>
-      <c r="BP153" s="5"/>
-      <c r="BQ153" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR153" s="5"/>
-      <c r="BS153" s="5"/>
-      <c r="BT153" s="5"/>
-      <c r="BU153" s="4" t="s">
+      <c r="BM153" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN153" s="24"/>
+      <c r="BO153" s="24"/>
+      <c r="BP153" s="24"/>
+      <c r="BQ153" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR153" s="24"/>
+      <c r="BS153" s="24"/>
+      <c r="BT153" s="24"/>
+      <c r="BU153" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="154" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A154" s="6" t="s">
+    <row r="154" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A154" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="B154" s="4">
+      <c r="B154" s="23">
         <v>300023</v>
       </c>
-      <c r="C154" s="5">
+      <c r="C154" s="24">
         <v>51.45</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154" s="23">
         <v>157.1166667</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="E154" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F154" s="4" t="s">
+      <c r="F154" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H154" s="4" t="s">
+      <c r="H154" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="I154" s="5"/>
-      <c r="J154" s="5"/>
-      <c r="K154" s="4"/>
-      <c r="L154" s="4">
+      <c r="I154" s="24"/>
+      <c r="J154" s="24"/>
+      <c r="K154" s="23"/>
+      <c r="L154" s="23">
         <v>8387</v>
       </c>
-      <c r="M154" s="4"/>
-      <c r="N154" s="4" t="s">
+      <c r="M154" s="23"/>
+      <c r="N154" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O154" s="4" t="s">
+      <c r="O154" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P154" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q154" s="5">
+      <c r="P154" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q154" s="24">
         <v>77</v>
       </c>
-      <c r="R154" s="5"/>
-      <c r="S154" s="5">
+      <c r="R154" s="24"/>
+      <c r="S154" s="24">
         <v>17</v>
       </c>
-      <c r="T154" s="5" t="s">
+      <c r="T154" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="U154" s="5">
+      <c r="U154" s="24">
         <v>33</v>
       </c>
-      <c r="V154" s="5"/>
-      <c r="W154" s="5">
+      <c r="V154" s="24"/>
+      <c r="W154" s="24">
         <v>7</v>
       </c>
-      <c r="X154" s="5" t="s">
+      <c r="X154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z154" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA154" s="5"/>
-      <c r="AB154" s="5"/>
-      <c r="AC154" s="5" t="s">
+      <c r="Y154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z154" s="24">
+        <v>45</v>
+      </c>
+      <c r="AA154" s="24"/>
+      <c r="AB154" s="24"/>
+      <c r="AC154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE154" s="5">
+      <c r="AD154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE154" s="24">
         <v>19.57</v>
       </c>
-      <c r="AF154" s="5"/>
-      <c r="AG154" s="5"/>
-      <c r="AH154" s="5" t="s">
+      <c r="AF154" s="24"/>
+      <c r="AG154" s="24"/>
+      <c r="AH154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ154" s="5">
+      <c r="AI154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ154" s="24">
         <v>18</v>
       </c>
-      <c r="AK154" s="5"/>
-      <c r="AL154" s="5"/>
-      <c r="AM154" s="5" t="s">
+      <c r="AK154" s="24"/>
+      <c r="AL154" s="24"/>
+      <c r="AM154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AN154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO154" s="5">
+      <c r="AN154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO154" s="24">
         <v>8</v>
       </c>
-      <c r="AP154" s="5"/>
-      <c r="AQ154" s="5"/>
-      <c r="AR154" s="5" t="s">
+      <c r="AP154" s="24"/>
+      <c r="AQ154" s="24"/>
+      <c r="AR154" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AS154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT154" s="5">
+      <c r="AS154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT154" s="24">
         <v>155</v>
       </c>
-      <c r="AU154" s="5"/>
-      <c r="AV154" s="5">
+      <c r="AU154" s="24"/>
+      <c r="AV154" s="24">
         <v>15</v>
       </c>
-      <c r="AW154" s="5">
+      <c r="AW154" s="24">
         <v>1</v>
       </c>
-      <c r="AX154" s="5" t="s">
+      <c r="AX154" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY154" s="5">
+      <c r="AY154" s="24">
         <v>75</v>
       </c>
-      <c r="AZ154" s="5"/>
-      <c r="BA154" s="5">
+      <c r="AZ154" s="24"/>
+      <c r="BA154" s="24">
         <v>5</v>
       </c>
-      <c r="BB154" s="5">
+      <c r="BB154" s="24">
         <v>1</v>
       </c>
-      <c r="BC154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD154" s="4" t="s">
+      <c r="BC154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD154" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="BE154" s="4"/>
-      <c r="BF154" s="5">
+      <c r="BE154" s="23"/>
+      <c r="BF154" s="24">
         <v>7.3</v>
       </c>
-      <c r="BG154" s="5"/>
-      <c r="BH154" s="5" t="s">
+      <c r="BG154" s="24"/>
+      <c r="BH154" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ154" s="5">
+      <c r="BI154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ154" s="24">
         <v>7</v>
       </c>
-      <c r="BK154" s="5"/>
-      <c r="BL154" s="5" t="s">
+      <c r="BK154" s="24"/>
+      <c r="BL154" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM154" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN154" s="5"/>
-      <c r="BO154" s="5"/>
-      <c r="BP154" s="5"/>
-      <c r="BQ154" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR154" s="5"/>
-      <c r="BS154" s="5"/>
-      <c r="BT154" s="5"/>
-      <c r="BU154" s="4" t="s">
+      <c r="BM154" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN154" s="24"/>
+      <c r="BO154" s="24"/>
+      <c r="BP154" s="24"/>
+      <c r="BQ154" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR154" s="24"/>
+      <c r="BS154" s="24"/>
+      <c r="BT154" s="24"/>
+      <c r="BU154" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="155" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A155" s="6" t="s">
+    <row r="155" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A155" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="B155" s="4">
+      <c r="B155" s="23">
         <v>300023</v>
       </c>
-      <c r="C155" s="5">
+      <c r="C155" s="24">
         <v>51.45</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155" s="23">
         <v>157.1166667</v>
       </c>
-      <c r="E155" s="5" t="s">
+      <c r="E155" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F155" s="4" t="s">
+      <c r="F155" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H155" s="4" t="s">
+      <c r="H155" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="I155" s="5"/>
-      <c r="J155" s="5"/>
-      <c r="K155" s="4"/>
-      <c r="L155" s="4">
+      <c r="I155" s="24"/>
+      <c r="J155" s="24"/>
+      <c r="K155" s="23"/>
+      <c r="L155" s="23">
         <v>8387</v>
       </c>
-      <c r="M155" s="4"/>
-      <c r="N155" s="4" t="s">
+      <c r="M155" s="23"/>
+      <c r="N155" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O155" s="4" t="s">
+      <c r="O155" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P155" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q155" s="5">
+      <c r="P155" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q155" s="24">
         <v>77</v>
       </c>
-      <c r="R155" s="5"/>
-      <c r="S155" s="5">
+      <c r="R155" s="24"/>
+      <c r="S155" s="24">
         <v>17</v>
       </c>
-      <c r="T155" s="5" t="s">
+      <c r="T155" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="U155" s="5">
+      <c r="U155" s="24">
         <v>33</v>
       </c>
-      <c r="V155" s="5"/>
-      <c r="W155" s="5">
+      <c r="V155" s="24"/>
+      <c r="W155" s="24">
         <v>7</v>
       </c>
-      <c r="X155" s="5" t="s">
+      <c r="X155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z155" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA155" s="5"/>
-      <c r="AB155" s="5"/>
-      <c r="AC155" s="5" t="s">
+      <c r="Y155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z155" s="24">
+        <v>45</v>
+      </c>
+      <c r="AA155" s="24"/>
+      <c r="AB155" s="24"/>
+      <c r="AC155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE155" s="5">
+      <c r="AD155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE155" s="24">
         <v>19.57</v>
       </c>
-      <c r="AF155" s="5"/>
-      <c r="AG155" s="5"/>
-      <c r="AH155" s="5" t="s">
+      <c r="AF155" s="24"/>
+      <c r="AG155" s="24"/>
+      <c r="AH155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ155" s="5">
+      <c r="AI155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ155" s="24">
         <v>18</v>
       </c>
-      <c r="AK155" s="5"/>
-      <c r="AL155" s="5"/>
-      <c r="AM155" s="5" t="s">
+      <c r="AK155" s="24"/>
+      <c r="AL155" s="24"/>
+      <c r="AM155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AN155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO155" s="5">
+      <c r="AN155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO155" s="24">
         <v>8</v>
       </c>
-      <c r="AP155" s="5"/>
-      <c r="AQ155" s="5"/>
-      <c r="AR155" s="5" t="s">
+      <c r="AP155" s="24"/>
+      <c r="AQ155" s="24"/>
+      <c r="AR155" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AS155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT155" s="5">
+      <c r="AS155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT155" s="24">
         <v>155</v>
       </c>
-      <c r="AU155" s="5"/>
-      <c r="AV155" s="5">
+      <c r="AU155" s="24"/>
+      <c r="AV155" s="24">
         <v>15</v>
       </c>
-      <c r="AW155" s="5">
+      <c r="AW155" s="24">
         <v>1</v>
       </c>
-      <c r="AX155" s="5" t="s">
+      <c r="AX155" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY155" s="5">
+      <c r="AY155" s="24">
         <v>75</v>
       </c>
-      <c r="AZ155" s="5"/>
-      <c r="BA155" s="5">
+      <c r="AZ155" s="24"/>
+      <c r="BA155" s="24">
         <v>5</v>
       </c>
-      <c r="BB155" s="5">
+      <c r="BB155" s="24">
         <v>1</v>
       </c>
-      <c r="BC155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD155" s="4" t="s">
+      <c r="BC155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD155" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="BE155" s="4"/>
-      <c r="BF155" s="5">
+      <c r="BE155" s="23"/>
+      <c r="BF155" s="24">
         <v>7.3</v>
       </c>
-      <c r="BG155" s="5"/>
-      <c r="BH155" s="5" t="s">
+      <c r="BG155" s="24"/>
+      <c r="BH155" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ155" s="5">
+      <c r="BI155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ155" s="24">
         <v>7</v>
       </c>
-      <c r="BK155" s="5"/>
-      <c r="BL155" s="5" t="s">
+      <c r="BK155" s="24"/>
+      <c r="BL155" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM155" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN155" s="5"/>
-      <c r="BO155" s="5"/>
-      <c r="BP155" s="5"/>
-      <c r="BQ155" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR155" s="5"/>
-      <c r="BS155" s="5"/>
-      <c r="BT155" s="5"/>
-      <c r="BU155" s="4" t="s">
+      <c r="BM155" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN155" s="24"/>
+      <c r="BO155" s="24"/>
+      <c r="BP155" s="24"/>
+      <c r="BQ155" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR155" s="24"/>
+      <c r="BS155" s="24"/>
+      <c r="BT155" s="24"/>
+      <c r="BU155" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="156" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A156" s="6" t="s">
+    <row r="156" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A156" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="B156" s="4">
+      <c r="B156" s="23">
         <v>300023</v>
       </c>
-      <c r="C156" s="5">
+      <c r="C156" s="24">
         <v>51.45</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156" s="23">
         <v>157.1166667</v>
       </c>
-      <c r="E156" s="5" t="s">
+      <c r="E156" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F156" s="4" t="s">
+      <c r="F156" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="G156" s="4" t="s">
+      <c r="G156" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H156" s="4" t="s">
+      <c r="H156" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="I156" s="5"/>
-      <c r="J156" s="5"/>
-      <c r="K156" s="4"/>
-      <c r="L156" s="4">
+      <c r="I156" s="24"/>
+      <c r="J156" s="24"/>
+      <c r="K156" s="23"/>
+      <c r="L156" s="23">
         <v>8387</v>
       </c>
-      <c r="M156" s="4"/>
-      <c r="N156" s="4" t="s">
+      <c r="M156" s="23"/>
+      <c r="N156" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O156" s="4" t="s">
+      <c r="O156" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P156" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q156" s="5">
+      <c r="P156" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q156" s="24">
         <v>77</v>
       </c>
-      <c r="R156" s="5"/>
-      <c r="S156" s="5">
+      <c r="R156" s="24"/>
+      <c r="S156" s="24">
         <v>17</v>
       </c>
-      <c r="T156" s="5" t="s">
+      <c r="T156" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="U156" s="5">
+      <c r="U156" s="24">
         <v>33</v>
       </c>
-      <c r="V156" s="5"/>
-      <c r="W156" s="5">
+      <c r="V156" s="24"/>
+      <c r="W156" s="24">
         <v>7</v>
       </c>
-      <c r="X156" s="5" t="s">
+      <c r="X156" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z156" s="5">
-        <v>45</v>
-      </c>
-      <c r="AA156" s="5"/>
-      <c r="AB156" s="5"/>
-      <c r="AC156" s="5" t="s">
+      <c r="Y156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z156" s="24">
+        <v>45</v>
+      </c>
+      <c r="AA156" s="24"/>
+      <c r="AB156" s="24"/>
+      <c r="AC156" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE156" s="5">
+      <c r="AD156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE156" s="24">
         <v>19.57</v>
       </c>
-      <c r="AF156" s="5"/>
-      <c r="AG156" s="5"/>
-      <c r="AH156" s="5" t="s">
+      <c r="AF156" s="24"/>
+      <c r="AG156" s="24"/>
+      <c r="AH156" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ156" s="5">
+      <c r="AI156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ156" s="24">
         <v>18</v>
       </c>
-      <c r="AK156" s="5"/>
-      <c r="AL156" s="5"/>
-      <c r="AM156" s="5" t="s">
+      <c r="AK156" s="24"/>
+      <c r="AL156" s="24"/>
+      <c r="AM156" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AN156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO156" s="5">
+      <c r="AN156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO156" s="24">
         <v>8</v>
       </c>
-      <c r="AP156" s="5"/>
-      <c r="AQ156" s="5"/>
-      <c r="AR156" s="5" t="s">
+      <c r="AP156" s="24"/>
+      <c r="AQ156" s="24"/>
+      <c r="AR156" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AS156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT156" s="5">
+      <c r="AS156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT156" s="24">
         <v>155</v>
       </c>
-      <c r="AU156" s="5"/>
-      <c r="AV156" s="5">
+      <c r="AU156" s="24"/>
+      <c r="AV156" s="24">
         <v>15</v>
       </c>
-      <c r="AW156" s="5">
+      <c r="AW156" s="24">
         <v>1</v>
       </c>
-      <c r="AX156" s="5" t="s">
+      <c r="AX156" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY156" s="5">
+      <c r="AY156" s="24">
         <v>75</v>
       </c>
-      <c r="AZ156" s="5"/>
-      <c r="BA156" s="5">
+      <c r="AZ156" s="24"/>
+      <c r="BA156" s="24">
         <v>5</v>
       </c>
-      <c r="BB156" s="5">
+      <c r="BB156" s="24">
         <v>1</v>
       </c>
-      <c r="BC156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD156" s="4" t="s">
+      <c r="BC156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD156" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="BE156" s="4"/>
-      <c r="BF156" s="5">
+      <c r="BE156" s="23"/>
+      <c r="BF156" s="24">
         <v>7.3</v>
       </c>
-      <c r="BG156" s="5"/>
-      <c r="BH156" s="5" t="s">
+      <c r="BG156" s="24"/>
+      <c r="BH156" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ156" s="5">
+      <c r="BI156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ156" s="24">
         <v>7</v>
       </c>
-      <c r="BK156" s="5"/>
-      <c r="BL156" s="5" t="s">
+      <c r="BK156" s="24"/>
+      <c r="BL156" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM156" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN156" s="5"/>
-      <c r="BO156" s="5"/>
-      <c r="BP156" s="5"/>
-      <c r="BQ156" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR156" s="5"/>
-      <c r="BS156" s="5"/>
-      <c r="BT156" s="5"/>
-      <c r="BU156" s="4" t="s">
+      <c r="BM156" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN156" s="24"/>
+      <c r="BO156" s="24"/>
+      <c r="BP156" s="24"/>
+      <c r="BQ156" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR156" s="24"/>
+      <c r="BS156" s="24"/>
+      <c r="BT156" s="24"/>
+      <c r="BU156" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="157" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A157" s="6" t="s">
+    <row r="157" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A157" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="B157" s="4">
+      <c r="B157" s="23">
         <v>322160</v>
       </c>
-      <c r="C157" s="5">
+      <c r="C157" s="24">
         <v>42.933333330000004</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157" s="23">
         <v>-122.1166667</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E157" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F157" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H157" s="4" t="s">
+      <c r="H157" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="I157" s="5"/>
-      <c r="J157" s="5"/>
-      <c r="K157" s="4">
+      <c r="I157" s="24"/>
+      <c r="J157" s="24"/>
+      <c r="K157" s="23">
         <v>-5783</v>
       </c>
-      <c r="L157" s="4">
+      <c r="L157" s="23">
         <v>7633</v>
       </c>
-      <c r="M157" s="4">
+      <c r="M157" s="23">
         <v>49</v>
       </c>
-      <c r="N157" s="4" t="s">
+      <c r="N157" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O157" s="4" t="s">
+      <c r="O157" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P157" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q157" s="5">
+      <c r="P157" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q157" s="24">
         <v>20</v>
       </c>
-      <c r="R157" s="5" t="s">
+      <c r="R157" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="S157" s="5"/>
-      <c r="T157" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U157" s="5">
+      <c r="S157" s="24"/>
+      <c r="T157" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="U157" s="24">
         <v>5</v>
       </c>
-      <c r="V157" s="5" t="s">
+      <c r="V157" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="W157" s="5"/>
-      <c r="X157" s="5" t="s">
+      <c r="W157" s="24"/>
+      <c r="X157" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y157" s="5" t="s">
+      <c r="Y157" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="Z157" s="5"/>
-      <c r="AA157" s="5"/>
-      <c r="AB157" s="5"/>
-      <c r="AC157" s="5"/>
-      <c r="AD157" s="5"/>
-      <c r="AE157" s="5"/>
-      <c r="AF157" s="5"/>
-      <c r="AG157" s="5"/>
-      <c r="AH157" s="5"/>
-      <c r="AI157" s="5"/>
-      <c r="AJ157" s="5">
+      <c r="Z157" s="24"/>
+      <c r="AA157" s="24"/>
+      <c r="AB157" s="24"/>
+      <c r="AC157" s="24"/>
+      <c r="AD157" s="24"/>
+      <c r="AE157" s="24"/>
+      <c r="AF157" s="24"/>
+      <c r="AG157" s="24"/>
+      <c r="AH157" s="24"/>
+      <c r="AI157" s="24"/>
+      <c r="AJ157" s="24">
         <v>19</v>
       </c>
-      <c r="AK157" s="5"/>
-      <c r="AL157" s="5"/>
-      <c r="AM157" s="5" t="s">
+      <c r="AK157" s="24"/>
+      <c r="AL157" s="24"/>
+      <c r="AM157" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AN157" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO157" s="5">
+      <c r="AN157" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO157" s="24">
         <v>7.9</v>
       </c>
-      <c r="AP157" s="5"/>
-      <c r="AQ157" s="5"/>
-      <c r="AR157" s="5" t="s">
+      <c r="AP157" s="24"/>
+      <c r="AQ157" s="24"/>
+      <c r="AR157" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AS157" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT157" s="5">
+      <c r="AS157" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT157" s="24">
         <v>120</v>
       </c>
-      <c r="AU157" s="5"/>
-      <c r="AV157" s="5"/>
-      <c r="AW157" s="5" t="s">
+      <c r="AU157" s="24"/>
+      <c r="AV157" s="24"/>
+      <c r="AW157" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AX157" s="5" t="s">
+      <c r="AX157" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY157" s="5">
+      <c r="AY157" s="24">
         <v>50</v>
       </c>
-      <c r="AZ157" s="5"/>
-      <c r="BA157" s="5"/>
-      <c r="BB157" s="5" t="s">
+      <c r="AZ157" s="24"/>
+      <c r="BA157" s="24"/>
+      <c r="BB157" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="BC157" s="5" t="s">
+      <c r="BC157" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD157" s="4" t="s">
+      <c r="BD157" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE157" s="4"/>
-      <c r="BF157" s="5">
+      <c r="BE157" s="23"/>
+      <c r="BF157" s="24">
         <v>7.1</v>
       </c>
-      <c r="BG157" s="5"/>
-      <c r="BH157" s="5" t="s">
+      <c r="BG157" s="24"/>
+      <c r="BH157" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI157" s="5" t="s">
+      <c r="BI157" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ157" s="5">
+      <c r="BJ157" s="24">
         <v>7</v>
       </c>
-      <c r="BK157" s="5"/>
-      <c r="BL157" s="5" t="s">
+      <c r="BK157" s="24"/>
+      <c r="BL157" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM157" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN157" s="5"/>
-      <c r="BO157" s="5">
+      <c r="BM157" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN157" s="24"/>
+      <c r="BO157" s="24">
         <v>55</v>
       </c>
-      <c r="BP157" s="5"/>
-      <c r="BQ157" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR157" s="5"/>
-      <c r="BS157" s="5">
+      <c r="BP157" s="24"/>
+      <c r="BQ157" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR157" s="24"/>
+      <c r="BS157" s="24">
         <v>12.3</v>
       </c>
-      <c r="BT157" s="5"/>
-      <c r="BU157" s="4" t="s">
+      <c r="BT157" s="24"/>
+      <c r="BU157" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="158" spans="1:73" s="3" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.2">
-      <c r="A158" s="6" t="s">
+    <row r="158" spans="1:73" s="25" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.2">
+      <c r="A158" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="B158" s="4">
+      <c r="B158" s="23">
         <v>282060</v>
       </c>
-      <c r="C158" s="5">
+      <c r="C158" s="24">
         <v>30.78944444</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158" s="23">
         <v>130.3075</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E158" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="F158" s="4" t="s">
+      <c r="F158" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="G158" s="4" t="s">
+      <c r="G158" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H158" s="4" t="s">
+      <c r="H158" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="I158" s="5"/>
-      <c r="J158" s="5"/>
-      <c r="K158" s="4"/>
-      <c r="L158" s="4">
+      <c r="I158" s="24"/>
+      <c r="J158" s="24"/>
+      <c r="K158" s="23"/>
+      <c r="L158" s="23">
         <v>7234</v>
       </c>
-      <c r="M158" s="4"/>
-      <c r="N158" s="4" t="s">
+      <c r="M158" s="23"/>
+      <c r="N158" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O158" s="4" t="s">
+      <c r="O158" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="P158" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q158" s="5">
+      <c r="P158" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q158" s="24">
         <v>140</v>
       </c>
-      <c r="R158" s="5"/>
-      <c r="S158" s="5"/>
-      <c r="T158" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U158" s="5">
+      <c r="R158" s="24"/>
+      <c r="S158" s="24"/>
+      <c r="T158" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="U158" s="24">
         <v>58</v>
       </c>
-      <c r="V158" s="5"/>
-      <c r="W158" s="5"/>
-      <c r="X158" s="5">
+      <c r="V158" s="24"/>
+      <c r="W158" s="24"/>
+      <c r="X158" s="24">
         <v>2</v>
       </c>
-      <c r="Y158" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z158" s="5">
+      <c r="Y158" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z158" s="24">
         <v>48</v>
       </c>
-      <c r="AA158" s="5"/>
-      <c r="AB158" s="5">
+      <c r="AA158" s="24"/>
+      <c r="AB158" s="24">
         <v>12</v>
       </c>
-      <c r="AC158" s="5" t="s">
+      <c r="AC158" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AD158" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE158" s="5">
+      <c r="AD158" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE158" s="24">
         <v>20</v>
       </c>
-      <c r="AF158" s="5"/>
-      <c r="AG158" s="5">
+      <c r="AF158" s="24"/>
+      <c r="AG158" s="24">
         <v>5</v>
       </c>
-      <c r="AH158" s="5">
+      <c r="AH158" s="24">
         <v>1</v>
       </c>
-      <c r="AI158" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ158" s="5"/>
-      <c r="AK158" s="5"/>
-      <c r="AL158" s="5"/>
-      <c r="AM158" s="5"/>
-      <c r="AN158" s="5"/>
-      <c r="AO158" s="5"/>
-      <c r="AP158" s="5"/>
-      <c r="AQ158" s="5"/>
-      <c r="AR158" s="5"/>
-      <c r="AS158" s="5"/>
-      <c r="AT158" s="5">
+      <c r="AI158" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ158" s="24"/>
+      <c r="AK158" s="24"/>
+      <c r="AL158" s="24"/>
+      <c r="AM158" s="24"/>
+      <c r="AN158" s="24"/>
+      <c r="AO158" s="24"/>
+      <c r="AP158" s="24"/>
+      <c r="AQ158" s="24"/>
+      <c r="AR158" s="24"/>
+      <c r="AS158" s="24"/>
+      <c r="AT158" s="24">
         <v>180</v>
       </c>
-      <c r="AU158" s="5"/>
-      <c r="AV158" s="5">
+      <c r="AU158" s="24"/>
+      <c r="AV158" s="24">
         <v>12</v>
       </c>
-      <c r="AW158" s="5" t="s">
+      <c r="AW158" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AX158" s="5" t="s">
+      <c r="AX158" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY158" s="5">
+      <c r="AY158" s="24">
         <v>75</v>
       </c>
-      <c r="AZ158" s="5"/>
-      <c r="BA158" s="5">
+      <c r="AZ158" s="24"/>
+      <c r="BA158" s="24">
         <v>5</v>
       </c>
-      <c r="BB158" s="5">
+      <c r="BB158" s="24">
         <v>1</v>
       </c>
-      <c r="BC158" s="5" t="s">
+      <c r="BC158" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD158" s="4" t="s">
+      <c r="BD158" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE158" s="4"/>
-      <c r="BF158" s="5">
+      <c r="BE158" s="23"/>
+      <c r="BF158" s="24">
         <v>7.3</v>
       </c>
-      <c r="BG158" s="5"/>
-      <c r="BH158" s="5" t="s">
+      <c r="BG158" s="24"/>
+      <c r="BH158" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI158" s="5" t="s">
+      <c r="BI158" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ158" s="5">
+      <c r="BJ158" s="24">
         <v>7</v>
       </c>
-      <c r="BK158" s="5"/>
-      <c r="BL158" s="5" t="s">
+      <c r="BK158" s="24"/>
+      <c r="BL158" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM158" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN158" s="5"/>
-      <c r="BO158" s="5">
+      <c r="BM158" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN158" s="24"/>
+      <c r="BO158" s="24">
         <v>43</v>
       </c>
-      <c r="BP158" s="5"/>
-      <c r="BQ158" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR158" s="5"/>
-      <c r="BS158" s="5">
+      <c r="BP158" s="24"/>
+      <c r="BQ158" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR158" s="24"/>
+      <c r="BS158" s="24">
         <v>11.83</v>
       </c>
-      <c r="BT158" s="5"/>
-      <c r="BU158" s="4" t="s">
+      <c r="BT158" s="24"/>
+      <c r="BU158" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="159" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A159" s="6" t="s">
+    <row r="159" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A159" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="B159" s="4">
+      <c r="B159" s="23">
         <v>242021</v>
       </c>
-      <c r="C159" s="5">
+      <c r="C159" s="24">
         <v>-30.2</v>
       </c>
-      <c r="D159" s="4">
+      <c r="D159" s="23">
         <v>-178.46666669999999</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E159" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="F159" s="4" t="s">
+      <c r="F159" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="G159" s="4" t="s">
+      <c r="G159" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H159" s="4" t="s">
+      <c r="H159" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="I159" s="5"/>
-      <c r="J159" s="5"/>
-      <c r="K159" s="4">
+      <c r="I159" s="24"/>
+      <c r="J159" s="24"/>
+      <c r="K159" s="23">
         <v>-5264</v>
       </c>
-      <c r="L159" s="4">
+      <c r="L159" s="23">
         <v>7214</v>
       </c>
-      <c r="M159" s="4"/>
-      <c r="N159" s="4" t="s">
+      <c r="M159" s="23"/>
+      <c r="N159" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O159" s="4" t="s">
+      <c r="O159" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="P159" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q159" s="5"/>
-      <c r="R159" s="5"/>
-      <c r="S159" s="5"/>
-      <c r="T159" s="5"/>
-      <c r="U159" s="5"/>
-      <c r="V159" s="5"/>
-      <c r="W159" s="5"/>
-      <c r="X159" s="5"/>
-      <c r="Y159" s="5"/>
-      <c r="Z159" s="5"/>
-      <c r="AA159" s="5"/>
-      <c r="AB159" s="5"/>
-      <c r="AC159" s="5"/>
-      <c r="AD159" s="5"/>
-      <c r="AE159" s="5"/>
-      <c r="AF159" s="5"/>
-      <c r="AG159" s="5"/>
-      <c r="AH159" s="5"/>
-      <c r="AI159" s="5"/>
-      <c r="AJ159" s="5"/>
-      <c r="AK159" s="5"/>
-      <c r="AL159" s="5"/>
-      <c r="AM159" s="5"/>
-      <c r="AN159" s="5"/>
-      <c r="AO159" s="5"/>
-      <c r="AP159" s="5"/>
-      <c r="AQ159" s="5"/>
-      <c r="AR159" s="5"/>
-      <c r="AS159" s="5"/>
-      <c r="AT159" s="5">
+      <c r="P159" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q159" s="24"/>
+      <c r="R159" s="24"/>
+      <c r="S159" s="24"/>
+      <c r="T159" s="24"/>
+      <c r="U159" s="24"/>
+      <c r="V159" s="24"/>
+      <c r="W159" s="24"/>
+      <c r="X159" s="24"/>
+      <c r="Y159" s="24"/>
+      <c r="Z159" s="24"/>
+      <c r="AA159" s="24"/>
+      <c r="AB159" s="24"/>
+      <c r="AC159" s="24"/>
+      <c r="AD159" s="24"/>
+      <c r="AE159" s="24"/>
+      <c r="AF159" s="24"/>
+      <c r="AG159" s="24"/>
+      <c r="AH159" s="24"/>
+      <c r="AI159" s="24"/>
+      <c r="AJ159" s="24"/>
+      <c r="AK159" s="24"/>
+      <c r="AL159" s="24"/>
+      <c r="AM159" s="24"/>
+      <c r="AN159" s="24"/>
+      <c r="AO159" s="24"/>
+      <c r="AP159" s="24"/>
+      <c r="AQ159" s="24"/>
+      <c r="AR159" s="24"/>
+      <c r="AS159" s="24"/>
+      <c r="AT159" s="24">
         <v>100</v>
       </c>
-      <c r="AU159" s="5" t="s">
+      <c r="AU159" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="AV159" s="5"/>
-      <c r="AW159" s="5">
+      <c r="AV159" s="24"/>
+      <c r="AW159" s="24">
         <v>1</v>
       </c>
-      <c r="AX159" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY159" s="5">
+      <c r="AX159" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY159" s="24">
         <v>41.7</v>
       </c>
-      <c r="AZ159" s="5" t="s">
+      <c r="AZ159" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="BA159" s="5"/>
-      <c r="BB159" s="5" t="s">
+      <c r="BA159" s="24"/>
+      <c r="BB159" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="BC159" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD159" s="4" t="s">
+      <c r="BC159" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD159" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE159" s="4"/>
-      <c r="BF159" s="5">
+      <c r="BE159" s="23"/>
+      <c r="BF159" s="24">
         <v>7</v>
       </c>
-      <c r="BG159" s="5" t="s">
+      <c r="BG159" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="BH159" s="5" t="s">
+      <c r="BH159" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI159" s="5" t="s">
+      <c r="BI159" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ159" s="5"/>
-      <c r="BK159" s="5"/>
-      <c r="BL159" s="5"/>
-      <c r="BM159" s="5"/>
-      <c r="BN159" s="5"/>
-      <c r="BO159" s="5"/>
-      <c r="BP159" s="5"/>
-      <c r="BQ159" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR159" s="5"/>
-      <c r="BS159" s="5"/>
-      <c r="BT159" s="5"/>
-      <c r="BU159" s="4" t="s">
+      <c r="BJ159" s="24"/>
+      <c r="BK159" s="24"/>
+      <c r="BL159" s="24"/>
+      <c r="BM159" s="24"/>
+      <c r="BN159" s="24"/>
+      <c r="BO159" s="24"/>
+      <c r="BP159" s="24"/>
+      <c r="BQ159" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR159" s="24"/>
+      <c r="BS159" s="24"/>
+      <c r="BT159" s="24"/>
+      <c r="BU159" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="160" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A160" s="6" t="s">
+    <row r="160" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A160" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B160" s="4">
+      <c r="B160" s="23">
         <v>355210</v>
       </c>
-      <c r="C160" s="5">
+      <c r="C160" s="24">
         <v>-26.766666666700001</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160" s="23">
         <v>-67.716666666699993</v>
       </c>
-      <c r="E160" s="5" t="s">
+      <c r="E160" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="F160" s="4" t="s">
+      <c r="F160" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="G160" s="4" t="s">
+      <c r="G160" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H160" s="4" t="s">
+      <c r="H160" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="I160" s="5"/>
-      <c r="J160" s="5"/>
-      <c r="K160" s="4"/>
-      <c r="L160" s="4">
+      <c r="I160" s="24"/>
+      <c r="J160" s="24"/>
+      <c r="K160" s="23"/>
+      <c r="L160" s="23">
         <v>4250</v>
       </c>
-      <c r="M160" s="4"/>
-      <c r="N160" s="4" t="s">
+      <c r="M160" s="23"/>
+      <c r="N160" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O160" s="4" t="s">
+      <c r="O160" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="P160" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q160" s="5"/>
-      <c r="R160" s="5"/>
-      <c r="S160" s="5"/>
-      <c r="T160" s="5"/>
-      <c r="U160" s="5"/>
-      <c r="V160" s="5"/>
-      <c r="W160" s="5"/>
-      <c r="X160" s="5"/>
-      <c r="Y160" s="5"/>
-      <c r="Z160" s="5"/>
-      <c r="AA160" s="5"/>
-      <c r="AB160" s="5"/>
-      <c r="AC160" s="5"/>
-      <c r="AD160" s="5"/>
-      <c r="AE160" s="5"/>
-      <c r="AF160" s="5"/>
-      <c r="AG160" s="5"/>
-      <c r="AH160" s="5"/>
-      <c r="AI160" s="5"/>
-      <c r="AJ160" s="5"/>
-      <c r="AK160" s="5"/>
-      <c r="AL160" s="5"/>
-      <c r="AM160" s="5"/>
-      <c r="AN160" s="5"/>
-      <c r="AO160" s="5"/>
-      <c r="AP160" s="5"/>
-      <c r="AQ160" s="5"/>
-      <c r="AR160" s="5"/>
-      <c r="AS160" s="5"/>
-      <c r="AT160" s="5">
+      <c r="P160" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q160" s="24"/>
+      <c r="R160" s="24"/>
+      <c r="S160" s="24"/>
+      <c r="T160" s="24"/>
+      <c r="U160" s="24"/>
+      <c r="V160" s="24"/>
+      <c r="W160" s="24"/>
+      <c r="X160" s="24"/>
+      <c r="Y160" s="24"/>
+      <c r="Z160" s="24"/>
+      <c r="AA160" s="24"/>
+      <c r="AB160" s="24"/>
+      <c r="AC160" s="24"/>
+      <c r="AD160" s="24"/>
+      <c r="AE160" s="24"/>
+      <c r="AF160" s="24"/>
+      <c r="AG160" s="24"/>
+      <c r="AH160" s="24"/>
+      <c r="AI160" s="24"/>
+      <c r="AJ160" s="24"/>
+      <c r="AK160" s="24"/>
+      <c r="AL160" s="24"/>
+      <c r="AM160" s="24"/>
+      <c r="AN160" s="24"/>
+      <c r="AO160" s="24"/>
+      <c r="AP160" s="24"/>
+      <c r="AQ160" s="24"/>
+      <c r="AR160" s="24"/>
+      <c r="AS160" s="24"/>
+      <c r="AT160" s="24">
         <v>110</v>
       </c>
-      <c r="AU160" s="5"/>
-      <c r="AV160" s="5"/>
-      <c r="AW160" s="5" t="s">
+      <c r="AU160" s="24"/>
+      <c r="AV160" s="24"/>
+      <c r="AW160" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AX160" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY160" s="5">
+      <c r="AX160" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY160" s="24">
         <v>48</v>
       </c>
-      <c r="AZ160" s="5"/>
-      <c r="BA160" s="5"/>
-      <c r="BB160" s="5" t="s">
+      <c r="AZ160" s="24"/>
+      <c r="BA160" s="24"/>
+      <c r="BB160" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="BC160" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD160" s="4" t="s">
+      <c r="BC160" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BD160" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="BE160" s="4"/>
-      <c r="BF160" s="5">
+      <c r="BE160" s="23"/>
+      <c r="BF160" s="24">
         <v>7</v>
       </c>
-      <c r="BG160" s="5"/>
-      <c r="BH160" s="5" t="s">
+      <c r="BG160" s="24"/>
+      <c r="BH160" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI160" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ160" s="5">
+      <c r="BI160" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ160" s="24">
         <v>7</v>
       </c>
-      <c r="BK160" s="5"/>
-      <c r="BL160" s="5" t="s">
+      <c r="BK160" s="24"/>
+      <c r="BL160" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BM160" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN160" s="5"/>
-      <c r="BO160" s="5"/>
-      <c r="BP160" s="5"/>
-      <c r="BQ160" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR160" s="5"/>
-      <c r="BS160" s="5"/>
-      <c r="BT160" s="5"/>
-      <c r="BU160" s="4" t="s">
+      <c r="BM160" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN160" s="24"/>
+      <c r="BO160" s="24"/>
+      <c r="BP160" s="24"/>
+      <c r="BQ160" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR160" s="24"/>
+      <c r="BS160" s="24"/>
+      <c r="BT160" s="24"/>
+      <c r="BU160" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="161" spans="1:73" s="3" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
-      <c r="A161" s="6" t="s">
+    <row r="161" spans="1:73" s="25" customFormat="1" ht="11.4" x14ac:dyDescent="0.2">
+      <c r="A161" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="B161" s="4">
+      <c r="B161" s="23">
         <v>212040</v>
       </c>
-      <c r="C161" s="5">
+      <c r="C161" s="24">
         <v>36.40361111</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161" s="23">
         <v>25.396388890000001</v>
       </c>
-      <c r="E161" s="5" t="s">
+      <c r="E161" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="F161" s="4" t="s">
+      <c r="F161" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="G161" s="4" t="s">
+      <c r="G161" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="H161" s="4" t="s">
+      <c r="H161" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="I161" s="5"/>
-      <c r="J161" s="5"/>
-      <c r="K161" s="4">
+      <c r="I161" s="24"/>
+      <c r="J161" s="24"/>
+      <c r="K161" s="23">
         <v>-1610</v>
       </c>
-      <c r="L161" s="4">
+      <c r="L161" s="23">
         <v>3560</v>
       </c>
-      <c r="M161" s="4">
+      <c r="M161" s="23">
         <v>14</v>
       </c>
-      <c r="N161" s="4" t="s">
+      <c r="N161" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O161" s="4" t="s">
+      <c r="O161" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P161" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q161" s="5">
+      <c r="P161" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q161" s="24">
         <v>1.2</v>
       </c>
-      <c r="R161" s="5"/>
-      <c r="S161" s="5"/>
-      <c r="T161" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U161" s="5">
+      <c r="R161" s="24"/>
+      <c r="S161" s="24"/>
+      <c r="T161" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="U161" s="24">
         <v>0.24</v>
       </c>
-      <c r="V161" s="5"/>
-      <c r="W161" s="5"/>
-      <c r="X161" s="5" t="s">
+      <c r="V161" s="24"/>
+      <c r="W161" s="24"/>
+      <c r="X161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y161" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z161" s="5">
+      <c r="Y161" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z161" s="24">
         <v>72</v>
       </c>
-      <c r="AA161" s="5"/>
-      <c r="AB161" s="5"/>
-      <c r="AC161" s="5" t="s">
+      <c r="AA161" s="24"/>
+      <c r="AB161" s="24"/>
+      <c r="AC161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD161" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE161" s="5">
+      <c r="AD161" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE161" s="24">
         <v>30.64</v>
       </c>
-      <c r="AF161" s="5"/>
-      <c r="AG161" s="5"/>
-      <c r="AH161" s="5" t="s">
+      <c r="AF161" s="24"/>
+      <c r="AG161" s="24"/>
+      <c r="AH161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI161" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ161" s="5">
+      <c r="AI161" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ161" s="24">
         <v>52.8</v>
       </c>
-      <c r="AK161" s="5"/>
-      <c r="AL161" s="5">
+      <c r="AK161" s="24"/>
+      <c r="AL161" s="24">
         <v>9.6</v>
       </c>
-      <c r="AM161" s="5" t="s">
+      <c r="AM161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AN161" s="5" t="s">
+      <c r="AN161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AO161" s="5">
+      <c r="AO161" s="24">
         <v>22</v>
       </c>
-      <c r="AP161" s="5"/>
-      <c r="AQ161" s="5">
+      <c r="AP161" s="24"/>
+      <c r="AQ161" s="24">
         <v>4</v>
       </c>
-      <c r="AR161" s="5" t="s">
+      <c r="AR161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AS161" s="5" t="s">
+      <c r="AS161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AT161" s="5">
+      <c r="AT161" s="24">
         <v>123</v>
       </c>
-      <c r="AU161" s="5"/>
-      <c r="AV161" s="5">
+      <c r="AU161" s="24"/>
+      <c r="AV161" s="24">
         <v>6</v>
       </c>
-      <c r="AW161" s="5" t="s">
+      <c r="AW161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AX161" s="5" t="s">
+      <c r="AX161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY161" s="5">
+      <c r="AY161" s="24">
         <v>82</v>
       </c>
-      <c r="AZ161" s="5"/>
-      <c r="BA161" s="5">
+      <c r="AZ161" s="24"/>
+      <c r="BA161" s="24">
         <v>4</v>
       </c>
-      <c r="BB161" s="5" t="s">
+      <c r="BB161" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="BC161" s="5" t="s">
+      <c r="BC161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD161" s="4" t="s">
+      <c r="BD161" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="BE161" s="4"/>
-      <c r="BF161" s="5">
+      <c r="BE161" s="23"/>
+      <c r="BF161" s="24">
         <v>7.3</v>
       </c>
-      <c r="BG161" s="5"/>
-      <c r="BH161" s="5" t="s">
+      <c r="BG161" s="24"/>
+      <c r="BH161" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BI161" s="5" t="s">
+      <c r="BI161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ161" s="5">
+      <c r="BJ161" s="24">
         <v>7</v>
       </c>
-      <c r="BK161" s="5"/>
-      <c r="BL161" s="5" t="s">
+      <c r="BK161" s="24"/>
+      <c r="BL161" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM161" s="5" t="s">
+      <c r="BM161" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BN161" s="5">
+      <c r="BN161" s="24">
         <v>20</v>
       </c>
-      <c r="BO161" s="5">
+      <c r="BO161" s="24">
         <v>36</v>
       </c>
-      <c r="BP161" s="5"/>
-      <c r="BQ161" s="4" t="s">
+      <c r="BP161" s="24"/>
+      <c r="BQ161" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="BR161" s="5">
+      <c r="BR161" s="24">
         <v>10.53</v>
       </c>
-      <c r="BS161" s="5">
+      <c r="BS161" s="24">
         <v>11.4</v>
       </c>
-      <c r="BT161" s="5"/>
-      <c r="BU161" s="4" t="s">
+      <c r="BT161" s="24"/>
+      <c r="BU161" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="162" spans="1:73" s="10" customFormat="1" ht="24" x14ac:dyDescent="0.3">
-      <c r="A162" s="6" t="s">
+    <row r="162" spans="1:73" s="26" customFormat="1" ht="24" x14ac:dyDescent="0.3">
+      <c r="A162" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B162" s="4">
+      <c r="B162" s="23">
         <v>305060</v>
       </c>
-      <c r="C162" s="5">
+      <c r="C162" s="24">
         <v>41.983333330000001</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162" s="23">
         <v>128.08333329999999</v>
       </c>
-      <c r="E162" s="5" t="s">
+      <c r="E162" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="F162" s="4" t="s">
+      <c r="F162" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G162" s="4" t="s">
+      <c r="G162" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H162" s="4" t="s">
+      <c r="H162" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="I162" s="5"/>
-      <c r="J162" s="5"/>
-      <c r="K162" s="4">
+      <c r="I162" s="24"/>
+      <c r="J162" s="24"/>
+      <c r="K162" s="23">
         <v>946</v>
       </c>
-      <c r="L162" s="4">
+      <c r="L162" s="23">
         <v>1004</v>
       </c>
-      <c r="M162" s="4"/>
-      <c r="N162" s="4" t="s">
+      <c r="M162" s="23"/>
+      <c r="N162" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="O162" s="4" t="s">
+      <c r="O162" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="P162" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q162" s="5">
+      <c r="P162" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q162" s="24">
         <v>100</v>
       </c>
-      <c r="R162" s="5"/>
-      <c r="S162" s="5"/>
-      <c r="T162" s="5" t="s">
+      <c r="R162" s="24"/>
+      <c r="S162" s="24"/>
+      <c r="T162" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="U162" s="5">
+      <c r="U162" s="24">
         <v>43.5</v>
       </c>
-      <c r="V162" s="5"/>
-      <c r="W162" s="5"/>
-      <c r="X162" s="5" t="s">
+      <c r="V162" s="24"/>
+      <c r="W162" s="24"/>
+      <c r="X162" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y162" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z162" s="5"/>
-      <c r="AA162" s="5"/>
-      <c r="AB162" s="5"/>
-      <c r="AC162" s="5"/>
-      <c r="AD162" s="5"/>
-      <c r="AE162" s="5"/>
-      <c r="AF162" s="5"/>
-      <c r="AG162" s="5"/>
-      <c r="AH162" s="5"/>
-      <c r="AI162" s="5"/>
-      <c r="AJ162" s="5"/>
-      <c r="AK162" s="5"/>
-      <c r="AL162" s="5"/>
-      <c r="AM162" s="5"/>
-      <c r="AN162" s="5"/>
-      <c r="AO162" s="5"/>
-      <c r="AP162" s="5"/>
-      <c r="AQ162" s="5"/>
-      <c r="AR162" s="5"/>
-      <c r="AS162" s="5"/>
-      <c r="AT162" s="5">
+      <c r="Y162" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z162" s="24"/>
+      <c r="AA162" s="24"/>
+      <c r="AB162" s="24"/>
+      <c r="AC162" s="24"/>
+      <c r="AD162" s="24"/>
+      <c r="AE162" s="24"/>
+      <c r="AF162" s="24"/>
+      <c r="AG162" s="24"/>
+      <c r="AH162" s="24"/>
+      <c r="AI162" s="24"/>
+      <c r="AJ162" s="24"/>
+      <c r="AK162" s="24"/>
+      <c r="AL162" s="24"/>
+      <c r="AM162" s="24"/>
+      <c r="AN162" s="24"/>
+      <c r="AO162" s="24"/>
+      <c r="AP162" s="24"/>
+      <c r="AQ162" s="24"/>
+      <c r="AR162" s="24"/>
+      <c r="AS162" s="24"/>
+      <c r="AT162" s="24">
         <v>100</v>
       </c>
-      <c r="AU162" s="5"/>
-      <c r="AV162" s="5"/>
-      <c r="AW162" s="5">
+      <c r="AU162" s="24"/>
+      <c r="AV162" s="24"/>
+      <c r="AW162" s="24">
         <v>0</v>
       </c>
-      <c r="AX162" s="5" t="s">
+      <c r="AX162" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY162" s="5">
+      <c r="AY162" s="24">
         <v>30</v>
       </c>
-      <c r="AZ162" s="5"/>
-      <c r="BA162" s="5"/>
-      <c r="BB162" s="5">
+      <c r="AZ162" s="24"/>
+      <c r="BA162" s="24"/>
+      <c r="BB162" s="24">
         <v>0</v>
       </c>
-      <c r="BC162" s="5" t="s">
+      <c r="BC162" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD162" s="4" t="s">
+      <c r="BD162" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="BE162" s="4"/>
-      <c r="BF162" s="5">
+      <c r="BE162" s="23"/>
+      <c r="BF162" s="24">
         <v>7.4</v>
       </c>
-      <c r="BG162" s="5"/>
-      <c r="BH162" s="5" t="s">
+      <c r="BG162" s="24"/>
+      <c r="BH162" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BI162" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ162" s="5">
+      <c r="BI162" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ162" s="24">
         <v>7</v>
       </c>
-      <c r="BK162" s="5"/>
-      <c r="BL162" s="5" t="s">
+      <c r="BK162" s="24"/>
+      <c r="BL162" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM162" s="5" t="s">
+      <c r="BM162" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BN162" s="5"/>
-      <c r="BO162" s="5">
+      <c r="BN162" s="24"/>
+      <c r="BO162" s="24">
         <v>25</v>
       </c>
-      <c r="BP162" s="5"/>
-      <c r="BQ162" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR162" s="5"/>
-      <c r="BS162" s="5">
+      <c r="BP162" s="24"/>
+      <c r="BQ162" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR162" s="24"/>
+      <c r="BS162" s="24">
         <v>10.9</v>
       </c>
-      <c r="BT162" s="5"/>
-      <c r="BU162" s="4" t="s">
+      <c r="BT162" s="24"/>
+      <c r="BU162" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="163" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="6" t="s">
+    <row r="163" spans="1:73" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="B163" s="4">
+      <c r="B163" s="23">
         <v>264030</v>
       </c>
-      <c r="C163" s="5">
+      <c r="C163" s="24">
         <v>-8.4166666669999994</v>
       </c>
-      <c r="D163" s="4">
+      <c r="D163" s="23">
         <v>116.4666667</v>
       </c>
-      <c r="E163" s="5" t="s">
+      <c r="E163" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="F163" s="4" t="s">
+      <c r="F163" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="G163" s="4" t="s">
+      <c r="G163" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H163" s="4" t="s">
+      <c r="H163" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="I163" s="5">
+      <c r="I163" s="24">
         <v>1</v>
       </c>
-      <c r="J163" s="5">
+      <c r="J163" s="24">
         <v>7</v>
       </c>
-      <c r="K163" s="4">
+      <c r="K163" s="23">
         <v>1257</v>
       </c>
-      <c r="L163" s="4">
+      <c r="L163" s="23">
         <v>693</v>
       </c>
-      <c r="M163" s="4"/>
-      <c r="N163" s="4" t="s">
+      <c r="M163" s="23"/>
+      <c r="N163" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="O163" s="4" t="s">
+      <c r="O163" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P163" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q163" s="5">
+      <c r="P163" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q163" s="24">
         <v>7.2</v>
       </c>
-      <c r="R163" s="5"/>
-      <c r="S163" s="5"/>
-      <c r="T163" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U163" s="5">
+      <c r="R163" s="24"/>
+      <c r="S163" s="24"/>
+      <c r="T163" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="U163" s="24">
         <v>3</v>
       </c>
-      <c r="V163" s="5"/>
-      <c r="W163" s="5"/>
-      <c r="X163" s="5" t="s">
+      <c r="V163" s="24"/>
+      <c r="W163" s="24"/>
+      <c r="X163" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y163" s="5" t="s">
+      <c r="Y163" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="Z163" s="5">
+      <c r="Z163" s="24">
         <v>16.8</v>
       </c>
-      <c r="AA163" s="5"/>
-      <c r="AB163" s="5"/>
-      <c r="AC163" s="5" t="s">
+      <c r="AA163" s="24"/>
+      <c r="AB163" s="24"/>
+      <c r="AC163" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD163" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE163" s="5">
+      <c r="AD163" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE163" s="24">
         <v>7</v>
       </c>
-      <c r="AF163" s="5"/>
-      <c r="AG163" s="5"/>
-      <c r="AH163" s="5" t="s">
+      <c r="AF163" s="24"/>
+      <c r="AG163" s="24"/>
+      <c r="AH163" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI163" s="5" t="s">
+      <c r="AI163" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AJ163" s="5"/>
-      <c r="AK163" s="5"/>
-      <c r="AL163" s="5"/>
-      <c r="AM163" s="5"/>
-      <c r="AN163" s="5"/>
-      <c r="AO163" s="5"/>
-      <c r="AP163" s="5"/>
-      <c r="AQ163" s="5"/>
-      <c r="AR163" s="5"/>
-      <c r="AS163" s="5"/>
-      <c r="AT163" s="5">
+      <c r="AJ163" s="24"/>
+      <c r="AK163" s="24"/>
+      <c r="AL163" s="24"/>
+      <c r="AM163" s="24"/>
+      <c r="AN163" s="24"/>
+      <c r="AO163" s="24"/>
+      <c r="AP163" s="24"/>
+      <c r="AQ163" s="24"/>
+      <c r="AR163" s="24"/>
+      <c r="AS163" s="24"/>
+      <c r="AT163" s="24">
         <v>91.25</v>
       </c>
-      <c r="AU163" s="5"/>
-      <c r="AV163" s="5">
+      <c r="AU163" s="24"/>
+      <c r="AV163" s="24">
         <v>8.75</v>
       </c>
-      <c r="AW163" s="5" t="s">
+      <c r="AW163" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AX163" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY163" s="5">
+      <c r="AX163" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY163" s="24">
         <v>36.5</v>
       </c>
-      <c r="AZ163" s="5"/>
-      <c r="BA163" s="5">
+      <c r="AZ163" s="24"/>
+      <c r="BA163" s="24">
         <v>3.5</v>
       </c>
-      <c r="BB163" s="5" t="s">
+      <c r="BB163" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="BC163" s="5" t="s">
+      <c r="BC163" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD163" s="4" t="s">
+      <c r="BD163" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BE163" s="4"/>
-      <c r="BF163" s="5">
+      <c r="BE163" s="23"/>
+      <c r="BF163" s="24">
         <v>7</v>
       </c>
-      <c r="BG163" s="5"/>
-      <c r="BH163" s="5" t="s">
+      <c r="BG163" s="24"/>
+      <c r="BH163" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BI163" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ163" s="5">
+      <c r="BI163" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BJ163" s="24">
         <v>7</v>
       </c>
-      <c r="BK163" s="5"/>
-      <c r="BL163" s="5" t="s">
+      <c r="BK163" s="24"/>
+      <c r="BL163" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM163" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN163" s="5"/>
-      <c r="BO163" s="5">
+      <c r="BM163" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN163" s="24"/>
+      <c r="BO163" s="24">
         <v>43</v>
       </c>
-      <c r="BP163" s="5"/>
-      <c r="BQ163" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR163" s="5"/>
-      <c r="BS163" s="5"/>
-      <c r="BT163" s="5"/>
-      <c r="BU163" s="4" t="s">
+      <c r="BP163" s="24"/>
+      <c r="BQ163" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR163" s="24"/>
+      <c r="BS163" s="24"/>
+      <c r="BT163" s="24"/>
+      <c r="BU163" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="164" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="6" t="s">
+    <row r="164" spans="1:73" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="B164" s="4">
+      <c r="B164" s="23">
         <v>257070</v>
       </c>
-      <c r="C164" s="5">
+      <c r="C164" s="24">
         <v>-16.829166669999999</v>
       </c>
-      <c r="D164" s="4">
+      <c r="D164" s="23">
         <v>168.5361111</v>
       </c>
-      <c r="E164" s="5" t="s">
+      <c r="E164" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="F164" s="4" t="s">
+      <c r="F164" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="G164" s="4" t="s">
+      <c r="G164" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H164" s="4" t="s">
+      <c r="H164" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="I164" s="5"/>
-      <c r="J164" s="5"/>
-      <c r="K164" s="4">
+      <c r="I164" s="24"/>
+      <c r="J164" s="24"/>
+      <c r="K164" s="23">
         <v>1452</v>
       </c>
-      <c r="L164" s="4">
+      <c r="L164" s="23">
         <v>498</v>
       </c>
-      <c r="M164" s="4"/>
-      <c r="N164" s="4" t="s">
+      <c r="M164" s="23"/>
+      <c r="N164" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="O164" s="4" t="s">
+      <c r="O164" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P164" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q164" s="5"/>
-      <c r="R164" s="5"/>
-      <c r="S164" s="5"/>
-      <c r="T164" s="5"/>
-      <c r="U164" s="5"/>
-      <c r="V164" s="5"/>
-      <c r="W164" s="5"/>
-      <c r="X164" s="5"/>
-      <c r="Y164" s="5"/>
-      <c r="Z164" s="5"/>
-      <c r="AA164" s="5"/>
-      <c r="AB164" s="5"/>
-      <c r="AC164" s="5"/>
-      <c r="AD164" s="5"/>
-      <c r="AE164" s="5"/>
-      <c r="AF164" s="5"/>
-      <c r="AG164" s="5"/>
-      <c r="AH164" s="5"/>
-      <c r="AI164" s="5"/>
-      <c r="AJ164" s="5">
+      <c r="P164" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q164" s="24"/>
+      <c r="R164" s="24"/>
+      <c r="S164" s="24"/>
+      <c r="T164" s="24"/>
+      <c r="U164" s="24"/>
+      <c r="V164" s="24"/>
+      <c r="W164" s="24"/>
+      <c r="X164" s="24"/>
+      <c r="Y164" s="24"/>
+      <c r="Z164" s="24"/>
+      <c r="AA164" s="24"/>
+      <c r="AB164" s="24"/>
+      <c r="AC164" s="24"/>
+      <c r="AD164" s="24"/>
+      <c r="AE164" s="24"/>
+      <c r="AF164" s="24"/>
+      <c r="AG164" s="24"/>
+      <c r="AH164" s="24"/>
+      <c r="AI164" s="24"/>
+      <c r="AJ164" s="24">
         <v>32.4</v>
       </c>
-      <c r="AK164" s="5"/>
-      <c r="AL164" s="5">
+      <c r="AK164" s="24"/>
+      <c r="AL164" s="24">
         <v>8.4</v>
       </c>
-      <c r="AM164" s="5" t="s">
+      <c r="AM164" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="AN164" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO164" s="5">
+      <c r="AN164" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO164" s="24">
         <v>13.5</v>
       </c>
-      <c r="AP164" s="5"/>
-      <c r="AQ164" s="5">
+      <c r="AP164" s="24"/>
+      <c r="AQ164" s="24">
         <v>3.5</v>
       </c>
-      <c r="AR164" s="5">
+      <c r="AR164" s="24">
         <v>1</v>
       </c>
-      <c r="AS164" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT164" s="5">
+      <c r="AS164" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AT164" s="24">
         <v>108</v>
       </c>
-      <c r="AU164" s="5"/>
-      <c r="AV164" s="5">
+      <c r="AU164" s="24"/>
+      <c r="AV164" s="24">
         <v>36</v>
       </c>
-      <c r="AW164" s="5">
+      <c r="AW164" s="24">
         <v>1</v>
       </c>
-      <c r="AX164" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY164" s="5">
-        <v>45</v>
-      </c>
-      <c r="AZ164" s="5"/>
-      <c r="BA164" s="5">
+      <c r="AX164" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AY164" s="24">
+        <v>45</v>
+      </c>
+      <c r="AZ164" s="24"/>
+      <c r="BA164" s="24">
         <v>15</v>
       </c>
-      <c r="BB164" s="5">
+      <c r="BB164" s="24">
         <v>1</v>
       </c>
-      <c r="BC164" s="5" t="s">
+      <c r="BC164" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD164" s="4" t="s">
+      <c r="BD164" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE164" s="4"/>
-      <c r="BF164" s="5">
+      <c r="BE164" s="23"/>
+      <c r="BF164" s="24">
         <v>7</v>
       </c>
-      <c r="BG164" s="5"/>
-      <c r="BH164" s="5" t="s">
+      <c r="BG164" s="24"/>
+      <c r="BH164" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="BI164" s="5" t="s">
+      <c r="BI164" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ164" s="5"/>
-      <c r="BK164" s="5"/>
-      <c r="BL164" s="5"/>
-      <c r="BM164" s="5"/>
-      <c r="BN164" s="5"/>
-      <c r="BO164" s="5"/>
-      <c r="BP164" s="5"/>
-      <c r="BQ164" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR164" s="5"/>
-      <c r="BS164" s="5"/>
-      <c r="BT164" s="5"/>
-      <c r="BU164" s="4" t="s">
+      <c r="BJ164" s="24"/>
+      <c r="BK164" s="24"/>
+      <c r="BL164" s="24"/>
+      <c r="BM164" s="24"/>
+      <c r="BN164" s="24"/>
+      <c r="BO164" s="24"/>
+      <c r="BP164" s="24"/>
+      <c r="BQ164" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR164" s="24"/>
+      <c r="BS164" s="24"/>
+      <c r="BT164" s="24"/>
+      <c r="BU164" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="165" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="6" t="s">
+    <row r="165" spans="1:73" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="B165" s="4">
+      <c r="B165" s="23">
         <v>264040</v>
       </c>
-      <c r="C165" s="5">
+      <c r="C165" s="24">
         <v>-8.25</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D165" s="23">
         <v>118</v>
       </c>
-      <c r="E165" s="5" t="s">
+      <c r="E165" s="24" t="s">
         <v>234</v>
       </c>
-      <c r="F165" s="4" t="s">
+      <c r="F165" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="G165" s="4" t="s">
+      <c r="G165" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="H165" s="4" t="s">
+      <c r="H165" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="I165" s="5"/>
-      <c r="J165" s="5"/>
-      <c r="K165" s="4">
+      <c r="I165" s="24"/>
+      <c r="J165" s="24"/>
+      <c r="K165" s="23">
         <v>1812</v>
       </c>
-      <c r="L165" s="4">
+      <c r="L165" s="23">
         <v>138</v>
       </c>
-      <c r="M165" s="4"/>
-      <c r="N165" s="4" t="s">
+      <c r="M165" s="23"/>
+      <c r="N165" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="O165" s="4" t="s">
+      <c r="O165" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P165" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q165" s="5">
+      <c r="P165" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q165" s="24">
         <v>101.3</v>
       </c>
-      <c r="R165" s="5"/>
-      <c r="S165" s="5"/>
-      <c r="T165" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U165" s="5">
+      <c r="R165" s="24"/>
+      <c r="S165" s="24"/>
+      <c r="T165" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="U165" s="24">
         <v>23</v>
       </c>
-      <c r="V165" s="5"/>
-      <c r="W165" s="5">
+      <c r="V165" s="24"/>
+      <c r="W165" s="24">
         <v>3</v>
       </c>
-      <c r="X165" s="5" t="s">
+      <c r="X165" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Y165" s="5" t="s">
+      <c r="Y165" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="Z165" s="5">
+      <c r="Z165" s="24">
         <v>5.7</v>
       </c>
-      <c r="AA165" s="5" t="s">
+      <c r="AA165" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="AB165" s="5"/>
-      <c r="AC165" s="5" t="s">
+      <c r="AB165" s="24"/>
+      <c r="AC165" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AD165" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE165" s="5">
+      <c r="AD165" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE165" s="24">
         <v>18</v>
       </c>
-      <c r="AF165" s="5"/>
-      <c r="AG165" s="5">
+      <c r="AF165" s="24"/>
+      <c r="AG165" s="24">
         <v>6</v>
       </c>
-      <c r="AH165" s="5" t="s">
+      <c r="AH165" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AI165" s="5" t="s">
+      <c r="AI165" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AJ165" s="5"/>
-      <c r="AK165" s="5"/>
-      <c r="AL165" s="5"/>
-      <c r="AM165" s="5"/>
-      <c r="AN165" s="5"/>
-      <c r="AO165" s="5"/>
-      <c r="AP165" s="5"/>
-      <c r="AQ165" s="5"/>
-      <c r="AR165" s="5"/>
-      <c r="AS165" s="5"/>
-      <c r="AT165" s="5">
+      <c r="AJ165" s="24"/>
+      <c r="AK165" s="24"/>
+      <c r="AL165" s="24"/>
+      <c r="AM165" s="24"/>
+      <c r="AN165" s="24"/>
+      <c r="AO165" s="24"/>
+      <c r="AP165" s="24"/>
+      <c r="AQ165" s="24"/>
+      <c r="AR165" s="24"/>
+      <c r="AS165" s="24"/>
+      <c r="AT165" s="24">
         <v>110</v>
       </c>
-      <c r="AU165" s="5"/>
-      <c r="AV165" s="5">
+      <c r="AU165" s="24"/>
+      <c r="AV165" s="24">
         <v>3</v>
       </c>
-      <c r="AW165" s="5" t="s">
+      <c r="AW165" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AX165" s="5" t="s">
+      <c r="AX165" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="AY165" s="5">
+      <c r="AY165" s="24">
         <v>41</v>
       </c>
-      <c r="AZ165" s="5"/>
-      <c r="BA165" s="5">
+      <c r="AZ165" s="24"/>
+      <c r="BA165" s="24">
         <v>4</v>
       </c>
-      <c r="BB165" s="5" t="s">
+      <c r="BB165" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="BC165" s="5" t="s">
+      <c r="BC165" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BD165" s="4" t="s">
+      <c r="BD165" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="BE165" s="4">
+      <c r="BE165" s="23">
         <v>2470</v>
       </c>
-      <c r="BF165" s="5">
+      <c r="BF165" s="24">
         <v>7</v>
       </c>
-      <c r="BG165" s="5"/>
-      <c r="BH165" s="5" t="s">
+      <c r="BG165" s="24"/>
+      <c r="BH165" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BI165" s="5" t="s">
+      <c r="BI165" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="BJ165" s="5">
+      <c r="BJ165" s="24">
         <v>7</v>
       </c>
-      <c r="BK165" s="5"/>
-      <c r="BL165" s="5" t="s">
+      <c r="BK165" s="24"/>
+      <c r="BL165" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="BM165" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN165" s="5">
+      <c r="BM165" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="BN165" s="24">
         <v>33</v>
       </c>
-      <c r="BO165" s="5">
+      <c r="BO165" s="24">
         <v>43</v>
       </c>
-      <c r="BP165" s="5"/>
-      <c r="BQ165" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="BR165" s="5"/>
-      <c r="BS165" s="5">
+      <c r="BP165" s="24"/>
+      <c r="BQ165" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="BR165" s="24"/>
+      <c r="BS165" s="24">
         <v>11.4</v>
       </c>
-      <c r="BT165" s="5"/>
-      <c r="BU165" s="4" t="s">
+      <c r="BT165" s="24"/>
+      <c r="BU165" s="23" t="s">
         <v>54</v>
       </c>
     </row>
@@ -25185,7 +25203,7 @@
       <c r="BU166" s="12"/>
     </row>
   </sheetData>
-  <sortState ref="A2:BU582">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:BU582">
     <sortCondition descending="1" ref="L2:L582"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
